--- a/새 폴더 (2)/data.xlsx
+++ b/새 폴더 (2)/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\360安全浏览器下载\새 폴더 (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393288BB-55E2-436E-AE81-AD56BE68D15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D0FB81-847A-4F3E-8522-CCEA21AABB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{DEA99F99-225F-4E99-9DC6-C46F1B2255DE}"/>
+    <workbookView xWindow="-28920" yWindow="1140" windowWidth="29040" windowHeight="15720" xr2:uid="{DEA99F99-225F-4E99-9DC6-C46F1B2255DE}"/>
   </bookViews>
   <sheets>
     <sheet name="계약이행율" sheetId="1" r:id="rId1"/>
@@ -412,7 +412,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="551">
   <si>
     <t>BIJT-C-LS-HK-25A-25-0071</t>
   </si>
@@ -2096,6 +2096,24 @@
   </si>
   <si>
     <t>BIJT-C-LS-HK-25A-26-0016</t>
+  </si>
+  <si>
+    <t>温州口腔医院有限公司连锁2</t>
+  </si>
+  <si>
+    <t>BIJT-C-LS-HK-25A-26-0018</t>
+  </si>
+  <si>
+    <t>四川齿康未来医疗器械有限公司2</t>
+  </si>
+  <si>
+    <t>BIJT-A-JX-HK-25A-26-0007</t>
+  </si>
+  <si>
+    <t>上海隆升和医疗科技有限公司2</t>
+  </si>
+  <si>
+    <t>BIJT-A-JX-HK-25A-26-0008</t>
   </si>
 </sst>
 </file>
@@ -2894,6 +2912,9 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2942,9 +2963,6 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -2954,27 +2972,7 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="3" xr:uid="{93B18076-440F-4C22-8412-54942F784DAC}"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3367,26 +3365,26 @@
       <c r="O1" s="7"/>
     </row>
     <row r="2" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="79" t="s">
         <v>494</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="81" t="s">
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="82" t="s">
         <v>495</v>
       </c>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="84" t="s">
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="85" t="s">
         <v>496</v>
       </c>
-      <c r="O2" s="85"/>
+      <c r="O2" s="86"/>
     </row>
     <row r="3" spans="1:15" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
@@ -3449,7 +3447,7 @@
       <c r="F4" s="19">
         <v>2</v>
       </c>
-      <c r="G4" s="94">
+      <c r="G4" s="78">
         <f>EDATE(E4,15)</f>
         <v>46161</v>
       </c>
@@ -3542,7 +3540,7 @@
       <c r="F6" s="19">
         <v>4</v>
       </c>
-      <c r="G6" s="94">
+      <c r="G6" s="78">
         <f t="shared" ref="G6:G9" si="2">EDATE(E6,15)</f>
         <v>46227</v>
       </c>
@@ -3589,7 +3587,7 @@
       <c r="F7" s="19">
         <v>2</v>
       </c>
-      <c r="G7" s="94">
+      <c r="G7" s="78">
         <f t="shared" si="2"/>
         <v>46163</v>
       </c>
@@ -3636,7 +3634,7 @@
       <c r="F8" s="19">
         <v>6</v>
       </c>
-      <c r="G8" s="94">
+      <c r="G8" s="78">
         <f t="shared" si="2"/>
         <v>46269</v>
       </c>
@@ -3683,7 +3681,7 @@
       <c r="F9" s="19">
         <v>4</v>
       </c>
-      <c r="G9" s="94">
+      <c r="G9" s="78">
         <f t="shared" si="2"/>
         <v>46233</v>
       </c>
@@ -3776,7 +3774,7 @@
       <c r="F11" s="19">
         <v>3</v>
       </c>
-      <c r="G11" s="94">
+      <c r="G11" s="78">
         <f t="shared" ref="G11:G14" si="3">EDATE(E11,15)</f>
         <v>46200</v>
       </c>
@@ -3823,7 +3821,7 @@
       <c r="F12" s="19">
         <v>3</v>
       </c>
-      <c r="G12" s="94">
+      <c r="G12" s="78">
         <f t="shared" si="3"/>
         <v>46185</v>
       </c>
@@ -3870,7 +3868,7 @@
       <c r="F13" s="19">
         <v>3</v>
       </c>
-      <c r="G13" s="94">
+      <c r="G13" s="78">
         <f t="shared" si="3"/>
         <v>46198</v>
       </c>
@@ -3917,7 +3915,7 @@
       <c r="F14" s="19">
         <v>5</v>
       </c>
-      <c r="G14" s="94">
+      <c r="G14" s="78">
         <f t="shared" si="3"/>
         <v>46263</v>
       </c>
@@ -4010,7 +4008,7 @@
       <c r="F16" s="19">
         <v>2</v>
       </c>
-      <c r="G16" s="94">
+      <c r="G16" s="78">
         <f t="shared" ref="G16:G25" si="4">EDATE(E16,15)</f>
         <v>46166</v>
       </c>
@@ -4057,7 +4055,7 @@
       <c r="F17" s="19">
         <v>3</v>
       </c>
-      <c r="G17" s="94">
+      <c r="G17" s="78">
         <f t="shared" si="4"/>
         <v>46185</v>
       </c>
@@ -4104,7 +4102,7 @@
       <c r="F18" s="19">
         <v>4</v>
       </c>
-      <c r="G18" s="94">
+      <c r="G18" s="78">
         <f t="shared" si="4"/>
         <v>46221</v>
       </c>
@@ -4151,7 +4149,7 @@
       <c r="F19" s="19">
         <v>4</v>
       </c>
-      <c r="G19" s="94">
+      <c r="G19" s="78">
         <f t="shared" si="4"/>
         <v>46226</v>
       </c>
@@ -4198,7 +4196,7 @@
       <c r="F20" s="19">
         <v>4</v>
       </c>
-      <c r="G20" s="94">
+      <c r="G20" s="78">
         <f t="shared" si="4"/>
         <v>46228</v>
       </c>
@@ -4245,7 +4243,7 @@
       <c r="F21" s="19">
         <v>2</v>
       </c>
-      <c r="G21" s="94">
+      <c r="G21" s="78">
         <f t="shared" si="4"/>
         <v>46163</v>
       </c>
@@ -4292,7 +4290,7 @@
       <c r="F22" s="19">
         <v>2</v>
       </c>
-      <c r="G22" s="94">
+      <c r="G22" s="78">
         <f t="shared" si="4"/>
         <v>46160</v>
       </c>
@@ -4339,7 +4337,7 @@
       <c r="F23" s="19">
         <v>6</v>
       </c>
-      <c r="G23" s="94">
+      <c r="G23" s="78">
         <f t="shared" si="4"/>
         <v>46292</v>
       </c>
@@ -4386,7 +4384,7 @@
       <c r="F24" s="19">
         <v>6</v>
       </c>
-      <c r="G24" s="94">
+      <c r="G24" s="78">
         <f t="shared" si="4"/>
         <v>46270</v>
       </c>
@@ -4433,7 +4431,7 @@
       <c r="F25" s="19">
         <v>7</v>
       </c>
-      <c r="G25" s="94">
+      <c r="G25" s="78">
         <f t="shared" si="4"/>
         <v>46296</v>
       </c>
@@ -4526,7 +4524,7 @@
       <c r="F27" s="19">
         <v>5</v>
       </c>
-      <c r="G27" s="94">
+      <c r="G27" s="78">
         <f t="shared" ref="G27:G28" si="5">EDATE(E27,15)</f>
         <v>46263</v>
       </c>
@@ -4573,7 +4571,7 @@
       <c r="F28" s="19">
         <v>3</v>
       </c>
-      <c r="G28" s="94">
+      <c r="G28" s="78">
         <f t="shared" si="5"/>
         <v>46187</v>
       </c>
@@ -4666,7 +4664,7 @@
       <c r="F30" s="19">
         <v>3</v>
       </c>
-      <c r="G30" s="94">
+      <c r="G30" s="78">
         <f t="shared" ref="G30:G34" si="6">EDATE(E30,15)</f>
         <v>46187</v>
       </c>
@@ -4713,7 +4711,7 @@
       <c r="F31" s="19">
         <v>8</v>
       </c>
-      <c r="G31" s="94">
+      <c r="G31" s="78">
         <f t="shared" si="6"/>
         <v>46339</v>
       </c>
@@ -4760,7 +4758,7 @@
       <c r="F32" s="19">
         <v>6</v>
       </c>
-      <c r="G32" s="94">
+      <c r="G32" s="78">
         <f t="shared" si="6"/>
         <v>46285</v>
       </c>
@@ -4807,7 +4805,7 @@
       <c r="F33" s="19">
         <v>4</v>
       </c>
-      <c r="G33" s="94">
+      <c r="G33" s="78">
         <f t="shared" si="6"/>
         <v>46230</v>
       </c>
@@ -4854,7 +4852,7 @@
       <c r="F34" s="19">
         <v>4</v>
       </c>
-      <c r="G34" s="94">
+      <c r="G34" s="78">
         <f t="shared" si="6"/>
         <v>46227</v>
       </c>
@@ -4947,7 +4945,7 @@
       <c r="F36" s="19">
         <v>10</v>
       </c>
-      <c r="G36" s="94">
+      <c r="G36" s="78">
         <f t="shared" ref="G36:G37" si="7">EDATE(E36,15)</f>
         <v>46415</v>
       </c>
@@ -4994,7 +4992,7 @@
       <c r="F37" s="19">
         <v>4</v>
       </c>
-      <c r="G37" s="94">
+      <c r="G37" s="78">
         <f t="shared" si="7"/>
         <v>46206</v>
       </c>
@@ -5133,7 +5131,7 @@
       <c r="F40" s="19">
         <v>3</v>
       </c>
-      <c r="G40" s="94">
+      <c r="G40" s="78">
         <f>EDATE(E40,15)</f>
         <v>46203</v>
       </c>
@@ -5226,7 +5224,7 @@
       <c r="F42" s="19">
         <v>8</v>
       </c>
-      <c r="G42" s="94">
+      <c r="G42" s="78">
         <f t="shared" ref="G42:G50" si="8">EDATE(E42,15)</f>
         <v>46334</v>
       </c>
@@ -5273,7 +5271,7 @@
       <c r="F43" s="19">
         <v>2</v>
       </c>
-      <c r="G43" s="94">
+      <c r="G43" s="78">
         <f t="shared" si="8"/>
         <v>46166</v>
       </c>
@@ -5320,7 +5318,7 @@
       <c r="F44" s="19">
         <v>7</v>
       </c>
-      <c r="G44" s="94">
+      <c r="G44" s="78">
         <f t="shared" si="8"/>
         <v>46325</v>
       </c>
@@ -5367,7 +5365,7 @@
       <c r="F45" s="19">
         <v>5</v>
       </c>
-      <c r="G45" s="94">
+      <c r="G45" s="78">
         <f t="shared" si="8"/>
         <v>46261</v>
       </c>
@@ -5414,7 +5412,7 @@
       <c r="F46" s="19">
         <v>5</v>
       </c>
-      <c r="G46" s="94">
+      <c r="G46" s="78">
         <f t="shared" si="8"/>
         <v>46247</v>
       </c>
@@ -5461,7 +5459,7 @@
       <c r="F47" s="19">
         <v>9</v>
       </c>
-      <c r="G47" s="94">
+      <c r="G47" s="78">
         <f t="shared" si="8"/>
         <v>46372</v>
       </c>
@@ -5508,7 +5506,7 @@
       <c r="F48" s="19">
         <v>5</v>
       </c>
-      <c r="G48" s="94">
+      <c r="G48" s="78">
         <f t="shared" si="8"/>
         <v>46249</v>
       </c>
@@ -5555,7 +5553,7 @@
       <c r="F49" s="19">
         <v>3</v>
       </c>
-      <c r="G49" s="94">
+      <c r="G49" s="78">
         <f t="shared" si="8"/>
         <v>46176</v>
       </c>
@@ -5602,7 +5600,7 @@
       <c r="F50" s="19">
         <v>3</v>
       </c>
-      <c r="G50" s="94">
+      <c r="G50" s="78">
         <f t="shared" si="8"/>
         <v>46192</v>
       </c>
@@ -5695,7 +5693,7 @@
       <c r="F52" s="19">
         <v>5</v>
       </c>
-      <c r="G52" s="94">
+      <c r="G52" s="78">
         <f t="shared" ref="G52:G53" si="9">EDATE(E52,15)</f>
         <v>46255</v>
       </c>
@@ -5742,7 +5740,7 @@
       <c r="F53" s="19">
         <v>4</v>
       </c>
-      <c r="G53" s="94">
+      <c r="G53" s="78">
         <f t="shared" si="9"/>
         <v>46204</v>
       </c>
@@ -5835,7 +5833,7 @@
       <c r="F55" s="19">
         <v>7</v>
       </c>
-      <c r="G55" s="94">
+      <c r="G55" s="78">
         <f t="shared" ref="G55:G62" si="10">EDATE(E55,15)</f>
         <v>46299</v>
       </c>
@@ -5882,7 +5880,7 @@
       <c r="F56" s="19">
         <v>3</v>
       </c>
-      <c r="G56" s="94">
+      <c r="G56" s="78">
         <f t="shared" si="10"/>
         <v>46198</v>
       </c>
@@ -5929,7 +5927,7 @@
       <c r="F57" s="19">
         <v>5</v>
       </c>
-      <c r="G57" s="94">
+      <c r="G57" s="78">
         <f t="shared" si="10"/>
         <v>46250</v>
       </c>
@@ -5976,7 +5974,7 @@
       <c r="F58" s="19">
         <v>8</v>
       </c>
-      <c r="G58" s="94">
+      <c r="G58" s="78">
         <f t="shared" si="10"/>
         <v>46345</v>
       </c>
@@ -6023,7 +6021,7 @@
       <c r="F59" s="19">
         <v>3</v>
       </c>
-      <c r="G59" s="94">
+      <c r="G59" s="78">
         <f t="shared" si="10"/>
         <v>46191</v>
       </c>
@@ -6070,7 +6068,7 @@
       <c r="F60" s="19">
         <v>5</v>
       </c>
-      <c r="G60" s="94">
+      <c r="G60" s="78">
         <f t="shared" si="10"/>
         <v>46248</v>
       </c>
@@ -6117,7 +6115,7 @@
       <c r="F61" s="19">
         <v>4</v>
       </c>
-      <c r="G61" s="94">
+      <c r="G61" s="78">
         <f t="shared" si="10"/>
         <v>46225</v>
       </c>
@@ -6164,7 +6162,7 @@
       <c r="F62" s="19">
         <v>3</v>
       </c>
-      <c r="G62" s="94">
+      <c r="G62" s="78">
         <f t="shared" si="10"/>
         <v>46179</v>
       </c>
@@ -6257,7 +6255,7 @@
       <c r="F64" s="19">
         <v>5</v>
       </c>
-      <c r="G64" s="94">
+      <c r="G64" s="78">
         <f t="shared" ref="G64:G66" si="11">EDATE(E64,15)</f>
         <v>46263</v>
       </c>
@@ -6304,7 +6302,7 @@
       <c r="F65" s="19">
         <v>3</v>
       </c>
-      <c r="G65" s="94">
+      <c r="G65" s="78">
         <f t="shared" si="11"/>
         <v>46198</v>
       </c>
@@ -6351,7 +6349,7 @@
       <c r="F66" s="19">
         <v>4</v>
       </c>
-      <c r="G66" s="94">
+      <c r="G66" s="78">
         <f t="shared" si="11"/>
         <v>46227</v>
       </c>
@@ -6444,7 +6442,7 @@
       <c r="F68" s="19">
         <v>4</v>
       </c>
-      <c r="G68" s="94">
+      <c r="G68" s="78">
         <f t="shared" ref="G68:G69" si="12">EDATE(E68,15)</f>
         <v>46213</v>
       </c>
@@ -6491,7 +6489,7 @@
       <c r="F69" s="19">
         <v>9</v>
       </c>
-      <c r="G69" s="94">
+      <c r="G69" s="78">
         <f t="shared" si="12"/>
         <v>46371</v>
       </c>
@@ -6584,7 +6582,7 @@
       <c r="F71" s="19">
         <v>3</v>
       </c>
-      <c r="G71" s="94">
+      <c r="G71" s="78">
         <f>EDATE(E71,15)</f>
         <v>46196</v>
       </c>
@@ -6723,7 +6721,7 @@
       <c r="F74" s="19">
         <v>3</v>
       </c>
-      <c r="G74" s="94">
+      <c r="G74" s="78">
         <f t="shared" ref="G74:G75" si="15">EDATE(E74,15)</f>
         <v>46198</v>
       </c>
@@ -6770,7 +6768,7 @@
       <c r="F75" s="19">
         <v>4</v>
       </c>
-      <c r="G75" s="94">
+      <c r="G75" s="78">
         <f t="shared" si="15"/>
         <v>46231</v>
       </c>
@@ -6909,7 +6907,7 @@
       <c r="F78" s="19">
         <v>3</v>
       </c>
-      <c r="G78" s="94">
+      <c r="G78" s="78">
         <f>EDATE(E78,15)</f>
         <v>46186</v>
       </c>
@@ -7002,7 +7000,7 @@
       <c r="F80" s="19">
         <v>5</v>
       </c>
-      <c r="G80" s="94">
+      <c r="G80" s="78">
         <f t="shared" ref="G80:G83" si="16">EDATE(E80,15)</f>
         <v>46248</v>
       </c>
@@ -7049,7 +7047,7 @@
       <c r="F81" s="19">
         <v>6</v>
       </c>
-      <c r="G81" s="94">
+      <c r="G81" s="78">
         <f t="shared" si="16"/>
         <v>46282</v>
       </c>
@@ -7097,7 +7095,7 @@
       <c r="F82" s="19">
         <v>6</v>
       </c>
-      <c r="G82" s="94">
+      <c r="G82" s="78">
         <f t="shared" si="16"/>
         <v>46290</v>
       </c>
@@ -7144,7 +7142,7 @@
       <c r="F83" s="19">
         <v>3</v>
       </c>
-      <c r="G83" s="94">
+      <c r="G83" s="78">
         <f t="shared" si="16"/>
         <v>46183</v>
       </c>
@@ -7237,7 +7235,7 @@
       <c r="F85" s="19">
         <v>4</v>
       </c>
-      <c r="G85" s="94">
+      <c r="G85" s="78">
         <f t="shared" ref="G85:G87" si="17">EDATE(E85,15)</f>
         <v>46228</v>
       </c>
@@ -7284,7 +7282,7 @@
       <c r="F86" s="19">
         <v>3</v>
       </c>
-      <c r="G86" s="94">
+      <c r="G86" s="78">
         <f t="shared" si="17"/>
         <v>46199</v>
       </c>
@@ -7331,7 +7329,7 @@
       <c r="F87" s="19">
         <v>6</v>
       </c>
-      <c r="G87" s="94">
+      <c r="G87" s="78">
         <f t="shared" si="17"/>
         <v>46282</v>
       </c>
@@ -7424,7 +7422,7 @@
       <c r="F89" s="19">
         <v>7</v>
       </c>
-      <c r="G89" s="94">
+      <c r="G89" s="78">
         <f>EDATE(E89,15)</f>
         <v>46311</v>
       </c>
@@ -7517,7 +7515,7 @@
       <c r="F91" s="19">
         <v>6</v>
       </c>
-      <c r="G91" s="94">
+      <c r="G91" s="78">
         <f t="shared" ref="G91:G92" si="18">EDATE(E91,15)</f>
         <v>46295</v>
       </c>
@@ -7564,7 +7562,7 @@
       <c r="F92" s="19">
         <v>5</v>
       </c>
-      <c r="G92" s="94">
+      <c r="G92" s="78">
         <f t="shared" si="18"/>
         <v>46253</v>
       </c>
@@ -7795,7 +7793,7 @@
       <c r="F97" s="19">
         <v>5</v>
       </c>
-      <c r="G97" s="94">
+      <c r="G97" s="78">
         <f t="shared" ref="G97:G98" si="19">EDATE(E97,15)</f>
         <v>46240</v>
       </c>
@@ -7842,7 +7840,7 @@
       <c r="F98" s="19">
         <v>3</v>
       </c>
-      <c r="G98" s="94">
+      <c r="G98" s="78">
         <f t="shared" si="19"/>
         <v>46203</v>
       </c>
@@ -7935,7 +7933,7 @@
       <c r="F100" s="19" t="s">
         <v>409</v>
       </c>
-      <c r="G100" s="94">
+      <c r="G100" s="78">
         <f>EDATE(E100,15)</f>
         <v>46491</v>
       </c>
@@ -8120,7 +8118,7 @@
       <c r="F104" s="19">
         <v>2</v>
       </c>
-      <c r="G104" s="94">
+      <c r="G104" s="78">
         <f>EDATE(E104,18)</f>
         <v>46262</v>
       </c>
@@ -8167,7 +8165,7 @@
       <c r="F105" s="19">
         <v>7</v>
       </c>
-      <c r="G105" s="94">
+      <c r="G105" s="78">
         <f t="shared" ref="G105" si="20">EDATE(E105,15)</f>
         <v>46316</v>
       </c>
@@ -8306,7 +8304,7 @@
       <c r="F108" s="19">
         <v>8</v>
       </c>
-      <c r="G108" s="94">
+      <c r="G108" s="78">
         <f t="shared" ref="G108:G109" si="21">EDATE(E108,15)</f>
         <v>46346</v>
       </c>
@@ -8353,7 +8351,7 @@
       <c r="F109" s="19">
         <v>5</v>
       </c>
-      <c r="G109" s="94">
+      <c r="G109" s="78">
         <f t="shared" si="21"/>
         <v>46260</v>
       </c>
@@ -8446,7 +8444,7 @@
       <c r="F111" s="19">
         <v>5</v>
       </c>
-      <c r="G111" s="94">
+      <c r="G111" s="78">
         <f t="shared" ref="G111:G112" si="22">EDATE(E111,15)</f>
         <v>46246</v>
       </c>
@@ -8493,7 +8491,7 @@
       <c r="F112" s="19">
         <v>4</v>
       </c>
-      <c r="G112" s="94">
+      <c r="G112" s="78">
         <f t="shared" si="22"/>
         <v>46206</v>
       </c>
@@ -8586,7 +8584,7 @@
       <c r="F114" s="19">
         <v>7</v>
       </c>
-      <c r="G114" s="94">
+      <c r="G114" s="78">
         <f>EDATE(E114,15)</f>
         <v>46306</v>
       </c>
@@ -8679,7 +8677,7 @@
       <c r="F116" s="19">
         <v>3</v>
       </c>
-      <c r="G116" s="94">
+      <c r="G116" s="78">
         <f t="shared" ref="G116:G117" si="23">EDATE(E116,15)</f>
         <v>46190</v>
       </c>
@@ -8726,7 +8724,7 @@
       <c r="F117" s="19">
         <v>5</v>
       </c>
-      <c r="G117" s="94">
+      <c r="G117" s="78">
         <f t="shared" si="23"/>
         <v>46254</v>
       </c>
@@ -8865,7 +8863,7 @@
       <c r="F120" s="19">
         <v>3</v>
       </c>
-      <c r="G120" s="94">
+      <c r="G120" s="78">
         <f>EDATE(E120,15)</f>
         <v>46190</v>
       </c>
@@ -8958,7 +8956,7 @@
       <c r="F122" s="19">
         <v>6</v>
       </c>
-      <c r="G122" s="94">
+      <c r="G122" s="78">
         <f t="shared" ref="G122:G125" si="24">EDATE(E122,15)</f>
         <v>46289</v>
       </c>
@@ -9005,7 +9003,7 @@
       <c r="F123" s="19">
         <v>10</v>
       </c>
-      <c r="G123" s="94">
+      <c r="G123" s="78">
         <f t="shared" si="24"/>
         <v>46408</v>
       </c>
@@ -9052,7 +9050,7 @@
       <c r="F124" s="19">
         <v>3</v>
       </c>
-      <c r="G124" s="94">
+      <c r="G124" s="78">
         <f t="shared" si="24"/>
         <v>46180</v>
       </c>
@@ -9099,7 +9097,7 @@
       <c r="F125" s="19">
         <v>9</v>
       </c>
-      <c r="G125" s="94">
+      <c r="G125" s="78">
         <f t="shared" si="24"/>
         <v>46375</v>
       </c>
@@ -9192,7 +9190,7 @@
       <c r="F127" s="19">
         <v>11</v>
       </c>
-      <c r="G127" s="94">
+      <c r="G127" s="78">
         <f>EDATE(E127,15)</f>
         <v>46429</v>
       </c>
@@ -9285,7 +9283,7 @@
       <c r="F129" s="19">
         <v>6</v>
       </c>
-      <c r="G129" s="94">
+      <c r="G129" s="78">
         <f>EDATE(E129,15)</f>
         <v>46292</v>
       </c>
@@ -9378,7 +9376,7 @@
       <c r="F131" s="19">
         <v>6</v>
       </c>
-      <c r="G131" s="94">
+      <c r="G131" s="78">
         <f>EDATE(E131,15)</f>
         <v>46274</v>
       </c>
@@ -9517,7 +9515,7 @@
       <c r="F134" s="19">
         <v>3</v>
       </c>
-      <c r="G134" s="94">
+      <c r="G134" s="78">
         <f>EDATE(E134,3)</f>
         <v>45835</v>
       </c>
@@ -9564,7 +9562,7 @@
       <c r="F135" s="19">
         <v>4</v>
       </c>
-      <c r="G135" s="94">
+      <c r="G135" s="78">
         <f t="shared" ref="G135:G139" si="27">EDATE(E135,15)</f>
         <v>46219</v>
       </c>
@@ -9611,7 +9609,7 @@
       <c r="F136" s="19">
         <v>4</v>
       </c>
-      <c r="G136" s="94">
+      <c r="G136" s="78">
         <f t="shared" si="27"/>
         <v>46219</v>
       </c>
@@ -9655,7 +9653,7 @@
       <c r="F137" s="19">
         <v>5</v>
       </c>
-      <c r="G137" s="94">
+      <c r="G137" s="78">
         <f t="shared" si="27"/>
         <v>46240</v>
       </c>
@@ -9702,7 +9700,7 @@
       <c r="F138" s="19">
         <v>5</v>
       </c>
-      <c r="G138" s="94">
+      <c r="G138" s="78">
         <f t="shared" si="27"/>
         <v>46253</v>
       </c>
@@ -9749,7 +9747,7 @@
       <c r="F139" s="19">
         <v>4</v>
       </c>
-      <c r="G139" s="94">
+      <c r="G139" s="78">
         <f t="shared" si="27"/>
         <v>46232</v>
       </c>
@@ -9842,7 +9840,7 @@
       <c r="F141" s="19">
         <v>3</v>
       </c>
-      <c r="G141" s="94">
+      <c r="G141" s="78">
         <f t="shared" ref="G141:G142" si="29">EDATE(E141,15)</f>
         <v>46197</v>
       </c>
@@ -9889,7 +9887,7 @@
       <c r="F142" s="19">
         <v>7</v>
       </c>
-      <c r="G142" s="94">
+      <c r="G142" s="78">
         <f t="shared" si="29"/>
         <v>46302</v>
       </c>
@@ -10012,7 +10010,7 @@
         <v>0.50660000000000005</v>
       </c>
     </row>
-    <row r="145" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B145" s="16" t="s">
         <v>207</v>
       </c>
@@ -10028,7 +10026,7 @@
       <c r="F145" s="19">
         <v>4</v>
       </c>
-      <c r="G145" s="94">
+      <c r="G145" s="78">
         <f t="shared" ref="G145:G147" si="30">EDATE(E145,15)</f>
         <v>46214</v>
       </c>
@@ -10075,7 +10073,7 @@
       <c r="F146" s="19">
         <v>7</v>
       </c>
-      <c r="G146" s="94">
+      <c r="G146" s="78">
         <f t="shared" si="30"/>
         <v>46302</v>
       </c>
@@ -10122,7 +10120,7 @@
       <c r="F147" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="G147" s="94">
+      <c r="G147" s="78">
         <f t="shared" si="30"/>
         <v>46543</v>
       </c>
@@ -10215,7 +10213,7 @@
       <c r="F149" s="19">
         <v>3</v>
       </c>
-      <c r="G149" s="94">
+      <c r="G149" s="78">
         <f t="shared" ref="G149:G212" si="31">EDATE(E149,15)</f>
         <v>46177</v>
       </c>
@@ -10262,7 +10260,7 @@
       <c r="F150" s="19">
         <v>5</v>
       </c>
-      <c r="G150" s="94">
+      <c r="G150" s="78">
         <f t="shared" si="31"/>
         <v>46254</v>
       </c>
@@ -10309,7 +10307,7 @@
       <c r="F151" s="19">
         <v>6</v>
       </c>
-      <c r="G151" s="94">
+      <c r="G151" s="78">
         <f t="shared" si="31"/>
         <v>46268</v>
       </c>
@@ -10356,7 +10354,7 @@
       <c r="F152" s="19">
         <v>4</v>
       </c>
-      <c r="G152" s="94">
+      <c r="G152" s="78">
         <f t="shared" si="31"/>
         <v>46226</v>
       </c>
@@ -10403,7 +10401,7 @@
       <c r="F153" s="19">
         <v>5</v>
       </c>
-      <c r="G153" s="94">
+      <c r="G153" s="78">
         <f t="shared" si="31"/>
         <v>46261</v>
       </c>
@@ -10450,7 +10448,7 @@
       <c r="F154" s="19">
         <v>6</v>
       </c>
-      <c r="G154" s="94">
+      <c r="G154" s="78">
         <f t="shared" si="31"/>
         <v>46275</v>
       </c>
@@ -10497,7 +10495,7 @@
       <c r="F155" s="19">
         <v>3</v>
       </c>
-      <c r="G155" s="94">
+      <c r="G155" s="78">
         <f t="shared" si="31"/>
         <v>46179</v>
       </c>
@@ -10544,7 +10542,7 @@
       <c r="F156" s="19">
         <v>10</v>
       </c>
-      <c r="G156" s="94">
+      <c r="G156" s="78">
         <f t="shared" si="31"/>
         <v>46416</v>
       </c>
@@ -10591,7 +10589,7 @@
       <c r="F157" s="19">
         <v>10</v>
       </c>
-      <c r="G157" s="94">
+      <c r="G157" s="78">
         <f t="shared" si="31"/>
         <v>46400</v>
       </c>
@@ -10638,7 +10636,7 @@
       <c r="F158" s="19">
         <v>9</v>
       </c>
-      <c r="G158" s="94">
+      <c r="G158" s="78">
         <f t="shared" si="31"/>
         <v>46382</v>
       </c>
@@ -10685,7 +10683,7 @@
       <c r="F159" s="19">
         <v>5</v>
       </c>
-      <c r="G159" s="94">
+      <c r="G159" s="78">
         <f t="shared" si="31"/>
         <v>46256</v>
       </c>
@@ -10732,7 +10730,7 @@
       <c r="F160" s="19">
         <v>3</v>
       </c>
-      <c r="G160" s="94">
+      <c r="G160" s="78">
         <f t="shared" si="31"/>
         <v>46186</v>
       </c>
@@ -10779,7 +10777,7 @@
       <c r="F161" s="19">
         <v>9</v>
       </c>
-      <c r="G161" s="94">
+      <c r="G161" s="78">
         <f t="shared" si="31"/>
         <v>46379</v>
       </c>
@@ -10826,7 +10824,7 @@
       <c r="F162" s="19" t="s">
         <v>409</v>
       </c>
-      <c r="G162" s="94">
+      <c r="G162" s="78">
         <f t="shared" si="31"/>
         <v>46498</v>
       </c>
@@ -10873,7 +10871,7 @@
       <c r="F163" s="19">
         <v>10</v>
       </c>
-      <c r="G163" s="94">
+      <c r="G163" s="78">
         <f t="shared" si="31"/>
         <v>46411</v>
       </c>
@@ -10920,7 +10918,7 @@
       <c r="F164" s="19">
         <v>9</v>
       </c>
-      <c r="G164" s="94">
+      <c r="G164" s="78">
         <f t="shared" si="31"/>
         <v>46366</v>
       </c>
@@ -10967,7 +10965,7 @@
       <c r="F165" s="19">
         <v>5</v>
       </c>
-      <c r="G165" s="94">
+      <c r="G165" s="78">
         <f t="shared" si="31"/>
         <v>46263</v>
       </c>
@@ -11014,7 +11012,7 @@
       <c r="F166" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="G166" s="94">
+      <c r="G166" s="78">
         <f t="shared" si="31"/>
         <v>46549</v>
       </c>
@@ -11061,7 +11059,7 @@
       <c r="F167" s="19">
         <v>4</v>
       </c>
-      <c r="G167" s="94">
+      <c r="G167" s="78">
         <f t="shared" si="31"/>
         <v>46232</v>
       </c>
@@ -11108,7 +11106,7 @@
       <c r="F168" s="19">
         <v>4</v>
       </c>
-      <c r="G168" s="94">
+      <c r="G168" s="78">
         <f t="shared" si="31"/>
         <v>46233</v>
       </c>
@@ -11155,7 +11153,7 @@
       <c r="F169" s="19" t="s">
         <v>409</v>
       </c>
-      <c r="G169" s="94">
+      <c r="G169" s="78">
         <f t="shared" si="31"/>
         <v>46491</v>
       </c>
@@ -11202,7 +11200,7 @@
       <c r="F170" s="19">
         <v>5</v>
       </c>
-      <c r="G170" s="94">
+      <c r="G170" s="78">
         <f t="shared" si="31"/>
         <v>46256</v>
       </c>
@@ -11249,7 +11247,7 @@
       <c r="F171" s="19">
         <v>6</v>
       </c>
-      <c r="G171" s="94">
+      <c r="G171" s="78">
         <f t="shared" si="31"/>
         <v>46285</v>
       </c>
@@ -11296,7 +11294,7 @@
       <c r="F172" s="19">
         <v>5</v>
       </c>
-      <c r="G172" s="94">
+      <c r="G172" s="78">
         <f t="shared" si="31"/>
         <v>46242</v>
       </c>
@@ -11343,7 +11341,7 @@
       <c r="F173" s="19">
         <v>3</v>
       </c>
-      <c r="G173" s="94">
+      <c r="G173" s="78">
         <f t="shared" si="31"/>
         <v>46183</v>
       </c>
@@ -11390,7 +11388,7 @@
       <c r="F174" s="19">
         <v>6</v>
       </c>
-      <c r="G174" s="94">
+      <c r="G174" s="78">
         <f t="shared" si="31"/>
         <v>46290</v>
       </c>
@@ -11437,7 +11435,7 @@
       <c r="F175" s="19">
         <v>3</v>
       </c>
-      <c r="G175" s="94">
+      <c r="G175" s="78">
         <f t="shared" si="31"/>
         <v>46198</v>
       </c>
@@ -11484,7 +11482,7 @@
       <c r="F176" s="19">
         <v>6</v>
       </c>
-      <c r="G176" s="94">
+      <c r="G176" s="78">
         <f t="shared" si="31"/>
         <v>46283</v>
       </c>
@@ -11531,7 +11529,7 @@
       <c r="F177" s="19">
         <v>5</v>
       </c>
-      <c r="G177" s="94">
+      <c r="G177" s="78">
         <f t="shared" si="31"/>
         <v>46247</v>
       </c>
@@ -11578,7 +11576,7 @@
       <c r="F178" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="G178" s="94">
+      <c r="G178" s="78">
         <f t="shared" si="31"/>
         <v>46517</v>
       </c>
@@ -11625,7 +11623,7 @@
       <c r="F179" s="19">
         <v>10</v>
       </c>
-      <c r="G179" s="94">
+      <c r="G179" s="78">
         <f t="shared" si="31"/>
         <v>46409</v>
       </c>
@@ -11672,7 +11670,7 @@
       <c r="F180" s="19">
         <v>12</v>
       </c>
-      <c r="G180" s="94">
+      <c r="G180" s="78">
         <f t="shared" si="31"/>
         <v>46469</v>
       </c>
@@ -11719,7 +11717,7 @@
       <c r="F181" s="19">
         <v>3</v>
       </c>
-      <c r="G181" s="94">
+      <c r="G181" s="78">
         <f t="shared" si="31"/>
         <v>46176</v>
       </c>
@@ -11766,7 +11764,7 @@
       <c r="F182" s="19">
         <v>12</v>
       </c>
-      <c r="G182" s="94">
+      <c r="G182" s="78">
         <f t="shared" si="31"/>
         <v>46465</v>
       </c>
@@ -11813,7 +11811,7 @@
       <c r="F183" s="19">
         <v>5</v>
       </c>
-      <c r="G183" s="94">
+      <c r="G183" s="78">
         <f t="shared" si="31"/>
         <v>46254</v>
       </c>
@@ -11860,7 +11858,7 @@
       <c r="F184" s="19">
         <v>8</v>
       </c>
-      <c r="G184" s="94">
+      <c r="G184" s="78">
         <f t="shared" si="31"/>
         <v>46352</v>
       </c>
@@ -11907,7 +11905,7 @@
       <c r="F185" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="G185" s="94">
+      <c r="G185" s="78">
         <f t="shared" si="31"/>
         <v>46532</v>
       </c>
@@ -11954,7 +11952,7 @@
       <c r="F186" s="19">
         <v>4</v>
       </c>
-      <c r="G186" s="94">
+      <c r="G186" s="78">
         <f t="shared" si="31"/>
         <v>46231</v>
       </c>
@@ -12001,7 +11999,7 @@
       <c r="F187" s="19">
         <v>9</v>
       </c>
-      <c r="G187" s="94">
+      <c r="G187" s="78">
         <f t="shared" si="31"/>
         <v>46364</v>
       </c>
@@ -12048,7 +12046,7 @@
       <c r="F188" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="G188" s="94">
+      <c r="G188" s="78">
         <f t="shared" si="31"/>
         <v>46596</v>
       </c>
@@ -12095,7 +12093,7 @@
       <c r="F189" s="19">
         <v>9</v>
       </c>
-      <c r="G189" s="94">
+      <c r="G189" s="78">
         <f t="shared" si="31"/>
         <v>46360</v>
       </c>
@@ -12142,7 +12140,7 @@
       <c r="F190" s="19">
         <v>5</v>
       </c>
-      <c r="G190" s="94">
+      <c r="G190" s="78">
         <f t="shared" si="31"/>
         <v>46243</v>
       </c>
@@ -12189,7 +12187,7 @@
       <c r="F191" s="19">
         <v>6</v>
       </c>
-      <c r="G191" s="94">
+      <c r="G191" s="78">
         <f t="shared" si="31"/>
         <v>46289</v>
       </c>
@@ -12236,7 +12234,7 @@
       <c r="F192" s="19">
         <v>5</v>
       </c>
-      <c r="G192" s="94">
+      <c r="G192" s="78">
         <f t="shared" si="31"/>
         <v>46248</v>
       </c>
@@ -12283,7 +12281,7 @@
       <c r="F193" s="19">
         <v>4</v>
       </c>
-      <c r="G193" s="94">
+      <c r="G193" s="78">
         <f t="shared" si="31"/>
         <v>46228</v>
       </c>
@@ -12330,7 +12328,7 @@
       <c r="F194" s="19">
         <v>3</v>
       </c>
-      <c r="G194" s="94">
+      <c r="G194" s="78">
         <f t="shared" si="31"/>
         <v>46186</v>
       </c>
@@ -12377,7 +12375,7 @@
       <c r="F195" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="G195" s="94">
+      <c r="G195" s="78">
         <f t="shared" si="31"/>
         <v>46585</v>
       </c>
@@ -12424,7 +12422,7 @@
       <c r="F196" s="19">
         <v>6</v>
       </c>
-      <c r="G196" s="94">
+      <c r="G196" s="78">
         <f t="shared" si="31"/>
         <v>46284</v>
       </c>
@@ -12471,7 +12469,7 @@
       <c r="F197" s="19">
         <v>5</v>
       </c>
-      <c r="G197" s="94">
+      <c r="G197" s="78">
         <f t="shared" si="31"/>
         <v>46249</v>
       </c>
@@ -12518,7 +12516,7 @@
       <c r="F198" s="19">
         <v>7</v>
       </c>
-      <c r="G198" s="94">
+      <c r="G198" s="78">
         <f t="shared" si="31"/>
         <v>46296</v>
       </c>
@@ -12565,7 +12563,7 @@
       <c r="F199" s="19">
         <v>7</v>
       </c>
-      <c r="G199" s="94">
+      <c r="G199" s="78">
         <f t="shared" si="31"/>
         <v>46296</v>
       </c>
@@ -12612,7 +12610,7 @@
       <c r="F200" s="19">
         <v>8</v>
       </c>
-      <c r="G200" s="94">
+      <c r="G200" s="78">
         <f t="shared" si="31"/>
         <v>46351</v>
       </c>
@@ -12660,7 +12658,7 @@
       <c r="F201" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="G201" s="94">
+      <c r="G201" s="78">
         <f t="shared" si="31"/>
         <v>46576</v>
       </c>
@@ -12707,7 +12705,7 @@
       <c r="F202" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="G202" s="94">
+      <c r="G202" s="78">
         <f t="shared" si="31"/>
         <v>46571</v>
       </c>
@@ -12754,7 +12752,7 @@
       <c r="F203" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="G203" s="94">
+      <c r="G203" s="78">
         <f t="shared" si="31"/>
         <v>46596</v>
       </c>
@@ -12801,7 +12799,7 @@
       <c r="F204" s="19">
         <v>6</v>
       </c>
-      <c r="G204" s="94">
+      <c r="G204" s="78">
         <f t="shared" si="31"/>
         <v>46295</v>
       </c>
@@ -12848,7 +12846,7 @@
       <c r="F205" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="G205" s="94">
+      <c r="G205" s="78">
         <f t="shared" si="31"/>
         <v>46564</v>
       </c>
@@ -12895,7 +12893,7 @@
       <c r="F206" s="19">
         <v>7</v>
       </c>
-      <c r="G206" s="94">
+      <c r="G206" s="78">
         <f t="shared" si="31"/>
         <v>46306</v>
       </c>
@@ -12942,7 +12940,7 @@
       <c r="F207" s="19">
         <v>11</v>
       </c>
-      <c r="G207" s="94">
+      <c r="G207" s="78">
         <f t="shared" si="31"/>
         <v>46423</v>
       </c>
@@ -12989,7 +12987,7 @@
       <c r="F208" s="19">
         <v>5</v>
       </c>
-      <c r="G208" s="94">
+      <c r="G208" s="78">
         <f t="shared" si="31"/>
         <v>46249</v>
       </c>
@@ -13036,7 +13034,7 @@
       <c r="F209" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="G209" s="94">
+      <c r="G209" s="78">
         <f t="shared" si="31"/>
         <v>46596</v>
       </c>
@@ -13083,7 +13081,7 @@
       <c r="F210" s="19">
         <v>5</v>
       </c>
-      <c r="G210" s="94">
+      <c r="G210" s="78">
         <f t="shared" si="31"/>
         <v>46263</v>
       </c>
@@ -13130,7 +13128,7 @@
       <c r="F211" s="19">
         <v>8</v>
       </c>
-      <c r="G211" s="94">
+      <c r="G211" s="78">
         <f t="shared" si="31"/>
         <v>46348</v>
       </c>
@@ -13177,7 +13175,7 @@
       <c r="F212" s="19">
         <v>5</v>
       </c>
-      <c r="G212" s="94">
+      <c r="G212" s="78">
         <f t="shared" si="31"/>
         <v>46241</v>
       </c>
@@ -13224,7 +13222,7 @@
       <c r="F213" s="19">
         <v>4</v>
       </c>
-      <c r="G213" s="94">
+      <c r="G213" s="78">
         <f t="shared" ref="G213:G246" si="34">EDATE(E213,15)</f>
         <v>46204</v>
       </c>
@@ -13271,7 +13269,7 @@
       <c r="F214" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="G214" s="94">
+      <c r="G214" s="78">
         <f t="shared" si="34"/>
         <v>46590</v>
       </c>
@@ -13318,7 +13316,7 @@
       <c r="F215" s="19">
         <v>4</v>
       </c>
-      <c r="G215" s="94">
+      <c r="G215" s="78">
         <f t="shared" si="34"/>
         <v>46233</v>
       </c>
@@ -13365,7 +13363,7 @@
       <c r="F216" s="19">
         <v>6</v>
       </c>
-      <c r="G216" s="94">
+      <c r="G216" s="78">
         <f t="shared" si="34"/>
         <v>46285</v>
       </c>
@@ -13412,7 +13410,7 @@
       <c r="F217" s="19">
         <v>6</v>
       </c>
-      <c r="G217" s="94">
+      <c r="G217" s="78">
         <f t="shared" si="34"/>
         <v>46288</v>
       </c>
@@ -13459,7 +13457,7 @@
       <c r="F218" s="19">
         <v>4</v>
       </c>
-      <c r="G218" s="94">
+      <c r="G218" s="78">
         <f t="shared" si="34"/>
         <v>46214</v>
       </c>
@@ -13506,7 +13504,7 @@
       <c r="F219" s="19">
         <v>9</v>
       </c>
-      <c r="G219" s="94">
+      <c r="G219" s="78">
         <f t="shared" si="34"/>
         <v>46378</v>
       </c>
@@ -13553,7 +13551,7 @@
       <c r="F220" s="19">
         <v>3</v>
       </c>
-      <c r="G220" s="94">
+      <c r="G220" s="78">
         <f t="shared" si="34"/>
         <v>46203</v>
       </c>
@@ -13600,7 +13598,7 @@
       <c r="F221" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="G221" s="94">
+      <c r="G221" s="78">
         <f t="shared" si="34"/>
         <v>46533</v>
       </c>
@@ -13647,7 +13645,7 @@
       <c r="F222" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="G222" s="94">
+      <c r="G222" s="78">
         <f t="shared" si="34"/>
         <v>46557</v>
       </c>
@@ -13694,7 +13692,7 @@
       <c r="F223" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="G223" s="94">
+      <c r="G223" s="78">
         <f t="shared" si="34"/>
         <v>46549</v>
       </c>
@@ -13741,7 +13739,7 @@
       <c r="F224" s="19">
         <v>7</v>
       </c>
-      <c r="G224" s="94">
+      <c r="G224" s="78">
         <f t="shared" si="34"/>
         <v>46313</v>
       </c>
@@ -13788,7 +13786,7 @@
       <c r="F225" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="G225" s="94">
+      <c r="G225" s="78">
         <f t="shared" si="34"/>
         <v>46568</v>
       </c>
@@ -13835,7 +13833,7 @@
       <c r="F226" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="G226" s="94">
+      <c r="G226" s="78">
         <f t="shared" si="34"/>
         <v>46562</v>
       </c>
@@ -13882,7 +13880,7 @@
       <c r="F227" s="19">
         <v>6</v>
       </c>
-      <c r="G227" s="94">
+      <c r="G227" s="78">
         <f t="shared" si="34"/>
         <v>46274</v>
       </c>
@@ -13929,7 +13927,7 @@
       <c r="F228" s="19">
         <v>5</v>
       </c>
-      <c r="G228" s="94">
+      <c r="G228" s="78">
         <f t="shared" si="34"/>
         <v>46242</v>
       </c>
@@ -13976,7 +13974,7 @@
       <c r="F229" s="19">
         <v>7</v>
       </c>
-      <c r="G229" s="94">
+      <c r="G229" s="78">
         <f t="shared" si="34"/>
         <v>46309</v>
       </c>
@@ -14023,7 +14021,7 @@
       <c r="F230" s="19">
         <v>3</v>
       </c>
-      <c r="G230" s="94">
+      <c r="G230" s="78">
         <f t="shared" si="34"/>
         <v>46176</v>
       </c>
@@ -14070,7 +14068,7 @@
       <c r="F231" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="G231" s="94">
+      <c r="G231" s="78">
         <f t="shared" si="34"/>
         <v>46554</v>
       </c>
@@ -14117,7 +14115,7 @@
       <c r="F232" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="G232" s="94">
+      <c r="G232" s="78">
         <f t="shared" si="34"/>
         <v>46569</v>
       </c>
@@ -14164,7 +14162,7 @@
       <c r="F233" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="G233" s="94">
+      <c r="G233" s="78">
         <f t="shared" si="34"/>
         <v>46596</v>
       </c>
@@ -14211,7 +14209,7 @@
       <c r="F234" s="19">
         <v>9</v>
       </c>
-      <c r="G234" s="94">
+      <c r="G234" s="78">
         <f t="shared" si="34"/>
         <v>46366</v>
       </c>
@@ -14258,7 +14256,7 @@
       <c r="F235" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="G235" s="94">
+      <c r="G235" s="78">
         <f t="shared" si="34"/>
         <v>46549</v>
       </c>
@@ -14302,7 +14300,7 @@
       <c r="F236" s="19">
         <v>6</v>
       </c>
-      <c r="G236" s="94">
+      <c r="G236" s="78">
         <f t="shared" si="34"/>
         <v>46271</v>
       </c>
@@ -14349,7 +14347,7 @@
       <c r="F237" s="19">
         <v>3</v>
       </c>
-      <c r="G237" s="94">
+      <c r="G237" s="78">
         <f t="shared" si="34"/>
         <v>46197</v>
       </c>
@@ -14396,7 +14394,7 @@
       <c r="F238" s="19">
         <v>7</v>
       </c>
-      <c r="G238" s="94">
+      <c r="G238" s="78">
         <f t="shared" si="34"/>
         <v>46312</v>
       </c>
@@ -14443,7 +14441,7 @@
       <c r="F239" s="19">
         <v>4</v>
       </c>
-      <c r="G239" s="94">
+      <c r="G239" s="78">
         <f t="shared" si="34"/>
         <v>46219</v>
       </c>
@@ -14490,7 +14488,7 @@
       <c r="F240" s="19" t="s">
         <v>511</v>
       </c>
-      <c r="G240" s="94">
+      <c r="G240" s="78">
         <f t="shared" si="34"/>
         <v>46571</v>
       </c>
@@ -14537,7 +14535,7 @@
       <c r="F241" s="19">
         <v>5</v>
       </c>
-      <c r="G241" s="94">
+      <c r="G241" s="78">
         <f t="shared" si="34"/>
         <v>46254</v>
       </c>
@@ -14584,7 +14582,7 @@
       <c r="F242" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="G242" s="94">
+      <c r="G242" s="78">
         <f t="shared" si="34"/>
         <v>46549</v>
       </c>
@@ -14631,7 +14629,7 @@
       <c r="F243" s="19" t="s">
         <v>530</v>
       </c>
-      <c r="G243" s="94">
+      <c r="G243" s="78">
         <f t="shared" si="34"/>
         <v>46605</v>
       </c>
@@ -14678,7 +14676,7 @@
       <c r="F244" s="19" t="s">
         <v>530</v>
       </c>
-      <c r="G244" s="94">
+      <c r="G244" s="78">
         <f t="shared" si="34"/>
         <v>46610</v>
       </c>
@@ -14725,7 +14723,7 @@
       <c r="F245" s="19" t="s">
         <v>530</v>
       </c>
-      <c r="G245" s="94">
+      <c r="G245" s="78">
         <f t="shared" si="34"/>
         <v>46612</v>
       </c>
@@ -14772,7 +14770,7 @@
       <c r="F246" s="19" t="s">
         <v>530</v>
       </c>
-      <c r="G246" s="94">
+      <c r="G246" s="78">
         <f t="shared" si="34"/>
         <v>46612</v>
       </c>
@@ -14815,8 +14813,14 @@
     <mergeCell ref="N2:O2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="B4:B199">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B201:B246">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B247:B1048576 B1:B3">
-    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:O1 N2 N3:O3 N247:O1048576">
     <cfRule type="dataBar" priority="12">
@@ -14885,12 +14889,6 @@
         </ext>
       </extLst>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B199">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B201:B246">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="56" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -14963,7 +14961,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79298CA-07B8-469C-8272-21CF31E320C4}">
-  <dimension ref="A1:P250"/>
+  <dimension ref="A1:P253"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" style="30" customWidth="1"/>
@@ -15015,26 +15013,26 @@
       <c r="F2" s="35" t="s">
         <v>430</v>
       </c>
-      <c r="G2" s="90" t="s">
+      <c r="G2" s="91" t="s">
         <v>520</v>
       </c>
-      <c r="H2" s="91"/>
-      <c r="I2" s="92" t="s">
+      <c r="H2" s="92"/>
+      <c r="I2" s="93" t="s">
         <v>522</v>
       </c>
-      <c r="J2" s="93"/>
-      <c r="K2" s="88" t="s">
+      <c r="J2" s="94"/>
+      <c r="K2" s="89" t="s">
         <v>521</v>
       </c>
-      <c r="L2" s="89"/>
-      <c r="M2" s="88" t="s">
+      <c r="L2" s="90"/>
+      <c r="M2" s="89" t="s">
         <v>431</v>
       </c>
-      <c r="N2" s="89"/>
-      <c r="O2" s="86" t="s">
+      <c r="N2" s="90"/>
+      <c r="O2" s="87" t="s">
         <v>523</v>
       </c>
-      <c r="P2" s="86" t="s">
+      <c r="P2" s="87" t="s">
         <v>524</v>
       </c>
     </row>
@@ -15068,8 +15066,8 @@
       <c r="N3" s="43" t="s">
         <v>433</v>
       </c>
-      <c r="O3" s="87"/>
-      <c r="P3" s="87"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
     </row>
     <row r="4" spans="2:16" s="46" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B4" s="44" t="s">
@@ -15079,47 +15077,37 @@
       <c r="D4" s="66"/>
       <c r="E4" s="66"/>
       <c r="F4" s="45">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="G4" s="45">
-        <f>SUM(G7:G266)</f>
-        <v>1516</v>
+        <v>1528</v>
       </c>
       <c r="H4" s="45">
-        <f t="shared" ref="H4:L4" si="0">SUM(H7:H266)</f>
-        <v>1124</v>
+        <v>1134</v>
       </c>
       <c r="I4" s="45">
-        <f>SUM(I5:I266)</f>
-        <v>773</v>
+        <v>784</v>
       </c>
       <c r="J4" s="45">
-        <f t="shared" si="0"/>
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="K4" s="67">
-        <f t="shared" si="0"/>
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="L4" s="68">
-        <f t="shared" si="0"/>
-        <v>878</v>
+        <v>861</v>
       </c>
       <c r="M4" s="69">
-        <f>I4/G4</f>
-        <v>0.50989445910290232</v>
+        <v>0.51308900523560208</v>
       </c>
       <c r="N4" s="69">
-        <f>J4/H4</f>
-        <v>0.2188612099644128</v>
+        <v>0.24074074074074073</v>
       </c>
       <c r="O4" s="70">
-        <f>SUM(O7:O1048576)</f>
-        <v>11560</v>
+        <v>11660</v>
       </c>
       <c r="P4" s="70">
-        <f>SUM(P7:P1048576)</f>
-        <v>58480</v>
+        <v>57820</v>
       </c>
     </row>
     <row r="5" spans="2:16" s="46" customFormat="1" ht="17" x14ac:dyDescent="0.3">
@@ -15128,7 +15116,7 @@
       </c>
       <c r="C5" s="47"/>
       <c r="D5" s="48">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E5" s="71"/>
       <c r="F5" s="49"/>
@@ -15944,25 +15932,25 @@
         <v>4</v>
       </c>
       <c r="J23" s="54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="54">
         <v>8</v>
       </c>
       <c r="L23" s="55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M23" s="56">
         <v>0.33333333333333331</v>
       </c>
       <c r="N23" s="56">
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="O23" s="54">
         <v>180</v>
       </c>
       <c r="P23" s="55">
-        <v>280</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
@@ -16129,28 +16117,28 @@
         <v>2</v>
       </c>
       <c r="I27" s="54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" s="54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" s="54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L27" s="55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" s="56">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N27" s="56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="54">
         <v>0</v>
       </c>
       <c r="P27" s="55">
-        <v>160</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
@@ -18812,25 +18800,25 @@
         <v>0</v>
       </c>
       <c r="J84" s="54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K84" s="54">
         <v>16</v>
       </c>
       <c r="L84" s="55">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M84" s="56">
         <v>0</v>
       </c>
       <c r="N84" s="56">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="O84" s="54">
         <v>0</v>
       </c>
       <c r="P84" s="55">
-        <v>960</v>
+        <v>880</v>
       </c>
     </row>
     <row r="85" spans="2:16" x14ac:dyDescent="0.3">
@@ -19470,25 +19458,25 @@
         <v>0</v>
       </c>
       <c r="J98" s="54">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K98" s="54">
         <v>8</v>
       </c>
       <c r="L98" s="55">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M98" s="56">
         <v>0</v>
       </c>
       <c r="N98" s="56">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O98" s="54">
         <v>0</v>
       </c>
       <c r="P98" s="55">
-        <v>480</v>
+        <v>320</v>
       </c>
     </row>
     <row r="99" spans="2:16" x14ac:dyDescent="0.3">
@@ -19564,25 +19552,25 @@
         <v>0</v>
       </c>
       <c r="J100" s="54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K100" s="54">
         <v>6</v>
       </c>
       <c r="L100" s="55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M100" s="56">
         <v>0</v>
       </c>
       <c r="N100" s="56">
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="O100" s="54">
         <v>0</v>
       </c>
       <c r="P100" s="55">
-        <v>360</v>
+        <v>280</v>
       </c>
     </row>
     <row r="101" spans="2:16" x14ac:dyDescent="0.3">
@@ -20316,25 +20304,25 @@
         <v>0</v>
       </c>
       <c r="J116" s="54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K116" s="54">
         <v>6</v>
       </c>
       <c r="L116" s="55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M116" s="56">
         <v>0</v>
       </c>
       <c r="N116" s="56">
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="O116" s="54">
         <v>0</v>
       </c>
       <c r="P116" s="55">
-        <v>360</v>
+        <v>280</v>
       </c>
     </row>
     <row r="117" spans="2:16" x14ac:dyDescent="0.3">
@@ -20880,25 +20868,25 @@
         <v>0</v>
       </c>
       <c r="J128" s="54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" s="54">
         <v>16</v>
       </c>
       <c r="L128" s="55">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M128" s="56">
         <v>0</v>
       </c>
       <c r="N128" s="56">
-        <v>0</v>
+        <v>6.25E-2</v>
       </c>
       <c r="O128" s="54">
         <v>0</v>
       </c>
       <c r="P128" s="55">
-        <v>960</v>
+        <v>920</v>
       </c>
     </row>
     <row r="129" spans="2:16" x14ac:dyDescent="0.3">
@@ -21820,25 +21808,25 @@
         <v>1</v>
       </c>
       <c r="J148" s="54">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K148" s="54">
         <v>7</v>
       </c>
       <c r="L148" s="55">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M148" s="56">
         <v>0.125</v>
       </c>
       <c r="N148" s="56">
-        <v>0.125</v>
+        <v>0.625</v>
       </c>
       <c r="O148" s="54">
         <v>60</v>
       </c>
       <c r="P148" s="55">
-        <v>420</v>
+        <v>260</v>
       </c>
     </row>
     <row r="149" spans="2:16" x14ac:dyDescent="0.3">
@@ -22052,28 +22040,28 @@
         <v>16</v>
       </c>
       <c r="I153" s="54">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J153" s="54">
         <v>8</v>
       </c>
       <c r="K153" s="54">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L153" s="55">
         <v>8</v>
       </c>
       <c r="M153" s="56">
-        <v>0.5</v>
+        <v>0.8125</v>
       </c>
       <c r="N153" s="56">
         <v>0.5</v>
       </c>
       <c r="O153" s="54">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P153" s="55">
-        <v>480</v>
+        <v>380</v>
       </c>
     </row>
     <row r="154" spans="2:16" x14ac:dyDescent="0.3">
@@ -22560,13 +22548,13 @@
         <v>10</v>
       </c>
       <c r="F164" s="53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G164" s="54">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H164" s="54">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I164" s="54">
         <v>0</v>
@@ -22575,22 +22563,22 @@
         <v>2</v>
       </c>
       <c r="K164" s="54">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L164" s="55">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M164" s="56">
         <v>0</v>
       </c>
       <c r="N164" s="56">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="O164" s="54">
         <v>0</v>
       </c>
       <c r="P164" s="55">
-        <v>880</v>
+        <v>400</v>
       </c>
     </row>
     <row r="165" spans="2:16" x14ac:dyDescent="0.3">
@@ -23136,25 +23124,25 @@
         <v>2</v>
       </c>
       <c r="J176" s="54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K176" s="54">
         <v>4</v>
       </c>
       <c r="L176" s="55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M176" s="56">
         <v>0.33333333333333331</v>
       </c>
       <c r="N176" s="56">
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="O176" s="54">
         <v>0</v>
       </c>
       <c r="P176" s="55">
-        <v>320</v>
+        <v>240</v>
       </c>
     </row>
     <row r="177" spans="2:16" x14ac:dyDescent="0.3">
@@ -23794,25 +23782,25 @@
         <v>0</v>
       </c>
       <c r="J190" s="54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K190" s="54">
         <v>4</v>
       </c>
       <c r="L190" s="55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M190" s="56">
         <v>0</v>
       </c>
       <c r="N190" s="56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O190" s="54">
         <v>0</v>
       </c>
       <c r="P190" s="55">
-        <v>160</v>
+        <v>80</v>
       </c>
     </row>
     <row r="191" spans="2:16" x14ac:dyDescent="0.3">
@@ -25486,25 +25474,25 @@
         <v>3</v>
       </c>
       <c r="J226" s="54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K226" s="54">
         <v>5</v>
       </c>
       <c r="L226" s="55">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M226" s="56">
         <v>0.375</v>
       </c>
       <c r="N226" s="56">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="O226" s="54">
         <v>0</v>
       </c>
       <c r="P226" s="55">
-        <v>420</v>
+        <v>340</v>
       </c>
     </row>
     <row r="227" spans="2:16" x14ac:dyDescent="0.3">
@@ -25530,19 +25518,19 @@
         <v>8</v>
       </c>
       <c r="I227" s="54">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J227" s="54">
         <v>0</v>
       </c>
       <c r="K227" s="54">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L227" s="55">
         <v>8</v>
       </c>
       <c r="M227" s="56">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N227" s="56">
         <v>0</v>
@@ -25551,7 +25539,7 @@
         <v>0</v>
       </c>
       <c r="P227" s="55">
-        <v>480</v>
+        <v>400</v>
       </c>
     </row>
     <row r="228" spans="2:16" x14ac:dyDescent="0.3">
@@ -26097,25 +26085,25 @@
         <v>0</v>
       </c>
       <c r="J239" s="54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K239" s="54">
         <v>8</v>
       </c>
       <c r="L239" s="55">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M239" s="56">
         <v>0</v>
       </c>
       <c r="N239" s="56">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="O239" s="54">
         <v>0</v>
       </c>
       <c r="P239" s="55">
-        <v>480</v>
+        <v>440</v>
       </c>
     </row>
     <row r="240" spans="2:16" x14ac:dyDescent="0.3">
@@ -26379,25 +26367,25 @@
         <v>0</v>
       </c>
       <c r="J245" s="53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K245" s="52">
         <v>8</v>
       </c>
       <c r="L245" s="61">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M245" s="30">
         <v>0</v>
       </c>
       <c r="N245" s="30">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="O245" s="32">
         <v>0</v>
       </c>
       <c r="P245" s="30">
-        <v>480</v>
+        <v>440</v>
       </c>
     </row>
     <row r="246" spans="2:16" x14ac:dyDescent="0.3">
@@ -26426,25 +26414,25 @@
         <v>0</v>
       </c>
       <c r="J246" s="53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K246" s="52">
         <v>8</v>
       </c>
       <c r="L246" s="61">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M246" s="30">
         <v>0</v>
       </c>
       <c r="N246" s="30">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="O246" s="32">
         <v>0</v>
       </c>
       <c r="P246" s="30">
-        <v>480</v>
+        <v>440</v>
       </c>
     </row>
     <row r="247" spans="2:16" x14ac:dyDescent="0.3">
@@ -26633,6 +26621,147 @@
       </c>
       <c r="P250" s="30">
         <v>160</v>
+      </c>
+    </row>
+    <row r="251" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B251" s="50" t="s">
+        <v>545</v>
+      </c>
+      <c r="C251" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D251" s="52" t="s">
+        <v>546</v>
+      </c>
+      <c r="E251" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="F251" s="53">
+        <v>1</v>
+      </c>
+      <c r="G251" s="53">
+        <v>4</v>
+      </c>
+      <c r="H251" s="53">
+        <v>2</v>
+      </c>
+      <c r="I251" s="53">
+        <v>0</v>
+      </c>
+      <c r="J251" s="53">
+        <v>0</v>
+      </c>
+      <c r="K251" s="52">
+        <v>4</v>
+      </c>
+      <c r="L251" s="61">
+        <v>2</v>
+      </c>
+      <c r="M251" s="30">
+        <v>0</v>
+      </c>
+      <c r="N251" s="30">
+        <v>0</v>
+      </c>
+      <c r="O251" s="32">
+        <v>0</v>
+      </c>
+      <c r="P251" s="30">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="252" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B252" s="50" t="s">
+        <v>547</v>
+      </c>
+      <c r="C252" s="60" t="s">
+        <v>133</v>
+      </c>
+      <c r="D252" s="52" t="s">
+        <v>548</v>
+      </c>
+      <c r="E252" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F252" s="53">
+        <v>1</v>
+      </c>
+      <c r="G252" s="53">
+        <v>8</v>
+      </c>
+      <c r="H252" s="53">
+        <v>8</v>
+      </c>
+      <c r="I252" s="53">
+        <v>0</v>
+      </c>
+      <c r="J252" s="53">
+        <v>0</v>
+      </c>
+      <c r="K252" s="52">
+        <v>8</v>
+      </c>
+      <c r="L252" s="61">
+        <v>8</v>
+      </c>
+      <c r="M252" s="30">
+        <v>0</v>
+      </c>
+      <c r="N252" s="30">
+        <v>0</v>
+      </c>
+      <c r="O252" s="32">
+        <v>0</v>
+      </c>
+      <c r="P252" s="30">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="253" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B253" s="50" t="s">
+        <v>549</v>
+      </c>
+      <c r="C253" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="D253" s="52" t="s">
+        <v>550</v>
+      </c>
+      <c r="E253" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F253" s="53">
+        <v>1</v>
+      </c>
+      <c r="G253" s="53">
+        <v>8</v>
+      </c>
+      <c r="H253" s="53">
+        <v>8</v>
+      </c>
+      <c r="I253" s="53">
+        <v>0</v>
+      </c>
+      <c r="J253" s="53">
+        <v>0</v>
+      </c>
+      <c r="K253" s="52">
+        <v>8</v>
+      </c>
+      <c r="L253" s="61">
+        <v>8</v>
+      </c>
+      <c r="M253" s="30">
+        <v>0</v>
+      </c>
+      <c r="N253" s="30">
+        <v>0</v>
+      </c>
+      <c r="O253" s="32">
+        <v>0</v>
+      </c>
+      <c r="P253" s="30">
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -26647,7 +26776,7 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B244:C1048576 B225 B1:C2 B4:C6 B7:B223 B230:B240">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
